--- a/Git和Gitee.xlsx
+++ b/Git和Gitee.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Git\violet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F627795-A3FB-4FE8-95EC-991BCAC2E6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB0BD3E-5C96-414B-AC33-937B8F008DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDE20AA2-380F-4E44-884D-4AB74603DCEE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>git config --global user.email "ambitiouschild.com"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,13 +235,997 @@
   <si>
     <t>选择yes</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用过程中，请确认【Pageant Key List】正在运行，且载入了对应私钥。</t>
+  </si>
+  <si>
+    <t>举例报错：Disconnected：No supported authentication methods availabled (server sent: publickey) 就是没有将步骤四中的私钥放进Pageant Key List中。每次电脑重启之后，就需要重新打开【Pageant】并添加私钥是不是很麻烦呢？请参阅，如何将私钥永久保存在Pageant Key List中？每次重启电脑都需要重新添加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动持久化 SSH 代理和密钥详解</t>
+  </si>
+  <si>
+    <r>
+      <t>在使用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4EA1DB"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>、远程服务器或其他依赖 SSH 认证的工具时，私钥是身份验证的核心。然而，很多用户在克隆、推送或拉取代码时，可能遇到如下错误：</t>
+    </r>
+  </si>
+  <si>
+    <t>这通常意味着 SSH 客户端无法找到对应的私钥文件，即使本地已正确配置 ~/.ssh/id_rsa 文件。其根本原因在于 SSH 代理 (ssh-agent) 重启后未能自动加载私钥。本文将从原理出发，讲解如何自动持久化 SSH 代理及其私钥，以避免每次服务器重启后手动执行 ssh-add。</t>
+  </si>
+  <si>
+    <r>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是一个运行在后台的守护进程，负责管理私钥并协助完成基于公钥的认证流程。默认情况下，它的生命周期与当前终端会话绑定。当服务器重启或会话关闭时，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 及其缓存的私钥会被清空。</t>
+    </r>
+  </si>
+  <si>
+    <t>SSH 代理的工作原理</t>
+  </si>
+  <si>
+    <t>1. 启动 SSH 代理</t>
+  </si>
+  <si>
+    <t>为什么重启服务器后需要重新执行？</t>
+  </si>
+  <si>
+    <r>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是临时进程，随系统重启而终止。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ssh-add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 添加的私钥仅在当前代理会话中有效。</t>
+    </r>
+  </si>
+  <si>
+    <t>默认未配置 SSH 代理的自启动及密钥的自动加载。</t>
+  </si>
+  <si>
+    <t>为解决上述问题，需手动配置 SSH 代理和私钥的持久化。</t>
+  </si>
+  <si>
+    <t>持久化 SSH 代理和密钥的方法</t>
+  </si>
+  <si>
+    <r>
+      <t>方案一：修改 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>~/.bashrc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4F4F4F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>（推荐）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>~/.bashrc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是 Bash Shell 登录时会自动执行的脚本文件，可用于初始化 SSH 代理。</t>
+    </r>
+  </si>
+  <si>
+    <t>1️⃣ 编辑文件</t>
+  </si>
+  <si>
+    <r>
+      <t>echo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"eval \</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFEE9900"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>$(ssh-agent -s)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA67F59"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.bashrc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>echo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ssh-add ~/.ssh/id_rsa"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA67F59"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.bashrc</t>
+    </r>
+  </si>
+  <si>
+    <t> 刷新配置</t>
+  </si>
+  <si>
+    <r>
+      <t>ource</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.bashrc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ssh-agent -s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：启动 SSH 代理。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ssh-add ~/.ssh/id_rsa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：将指定私钥加载到代理。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>该配置仅对当前用户有效，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>每次登录时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 自动生效。</t>
+    </r>
+  </si>
+  <si>
+    <t>注意事项</t>
+  </si>
+  <si>
+    <t>私钥文件需设定正确的权限：</t>
+  </si>
+  <si>
+    <r>
+      <t>chmod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF986801"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.ssh/id_rsa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t> 方案二：配置 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>~/.ssh/environment</t>
+    </r>
+  </si>
+  <si>
+    <t>这种方法适用于需要在不同终端会话中共享 SSH 代理的场景。</t>
+  </si>
+  <si>
+    <t>创建文件</t>
+  </si>
+  <si>
+    <r>
+      <t>mkdir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> -p ~/.ssh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>touch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.ssh/environment</t>
+    </r>
+  </si>
+  <si>
+    <t> 编写脚本</t>
+  </si>
+  <si>
+    <r>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF999999"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> -z </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF986801"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>$SSH_AUTH_SOCK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF999999"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0077AA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>eval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFEE9900"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>$(ssh-agent -s)</t>
+    </r>
+  </si>
+  <si>
+    <t>ssh-add ~/.ssh/id_rsa</t>
+  </si>
+  <si>
+    <t>fi</t>
+  </si>
+  <si>
+    <t>设置权限</t>
+  </si>
+  <si>
+    <r>
+      <t>chmod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF986801"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ~/.ssh/environment</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>检查环境变量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SSH_AUTH_SOCK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是否已定义，未定义则启动代理并加载私钥。</t>
+    </r>
+  </si>
+  <si>
+    <t>该方法确保新会话可继承 SSH 代理的配置。</t>
+  </si>
+  <si>
+    <r>
+      <t>方案三：配置 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4F4F4F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 服务（高级方案）</t>
+    </r>
+  </si>
+  <si>
+    <t> 创建服务文件</t>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDD4A68"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>nano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> /etc/systemd/system/ssh-agent.service</t>
+    </r>
+  </si>
+  <si>
+    <t>[Unit]
+Description=SSH Agent
+After=network.target
+[Service]
+User=username
+ExecStart=/usr/bin/ssh-agent -D
+Restart=always
+[Install]
+WantedBy=default.target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加以下内容</t>
+  </si>
+  <si>
+    <t>启动并启用服务</t>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> systemctl daemon-reload</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> systemctl </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF50A14F"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>enable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ssh-agent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> systemctl start ssh-agent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 会在系统启动时启动 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>需手动执行 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 一次以将密钥加入代理。</t>
+    </r>
+  </si>
+  <si>
+    <t> 多个 SSH 密钥冲突</t>
+  </si>
+  <si>
+    <r>
+      <t> 多个 SSH 私钥文件存在时，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 无法正确识别。</t>
+    </r>
+  </si>
+  <si>
+    <t>解决方案：</t>
+  </si>
+  <si>
+    <t>指定主机对应的私钥：</t>
+  </si>
+  <si>
+    <t>Host gitee.com IdentityFile ~/.ssh/id_rsa_gitee</t>
+  </si>
+  <si>
+    <r>
+      <t>配置完成后，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 会根据 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Host</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 选择对应的私钥。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ssh-agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 是 SSH 客户端认证的关键工具，需手动启动和加载私钥。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>服务器重启后需重新加载私钥，可通过 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>~/.bashrc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>~/.ssh/environment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 或 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 实现自动化。</t>
+    </r>
+  </si>
+  <si>
+    <t>合理设置私钥权限，避免因权限过大导致的认证失败。</t>
+  </si>
+  <si>
+    <r>
+      <t>可在服务器重启后，无需再次手动执行 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC7254E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ssh-add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4D4D4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，轻松实现 SSH 代理和私钥的持久化。</t>
+    </r>
+  </si>
+  <si>
+    <t>Git Bash是一个在Windows上提供类Unix命令行的工具，它通常包含一个类似于Linux的bash环境。你可以按照上述类似步骤操作：</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +1286,97 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4EA1DB"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC7254E"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FFC7254E"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF50A14F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA67F59"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFDD4A68"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF986801"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0077AA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -329,7 +1404,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -349,6 +1424,51 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F028FA-3DEB-4908-A20B-A8637E5E3B0B}">
-  <dimension ref="B4:B23"/>
+  <dimension ref="B4:E103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="78.5" customWidth="1"/>
@@ -875,6 +1995,319 @@
         <v>10</v>
       </c>
     </row>
+    <row r="25" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="57" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B31" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="B35" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B37" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B39" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="B41" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B42" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B43" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B45" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="B47" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="B48" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B49" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B50" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B51" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B52" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B53" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B54" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B56" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B57" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B58" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B59" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B60" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B61" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="B63" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B64" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B66" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B67" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B68" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B69" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B70" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B71" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B72" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B73" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B74" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B75" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B76" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B77" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="B79" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B80" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B81" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B82" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="B83" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B84" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B85" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B86" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B87" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B89" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B90" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B92" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B93" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B94" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B95" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B97" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B98" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B100" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" ht="30.75" x14ac:dyDescent="0.2">
+      <c r="B101" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B102" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B103" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
